--- a/04_DESIGN_TABLES/DesignTable_6504_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6504_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE11"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1077,35 +1077,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6504-06-06</t>
+          <t>6504-04-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="C4" t="n">
-        <v>0.36373</v>
+        <v>0.32447</v>
       </c>
       <c r="D4" t="n">
-        <v>0.63</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="K4" t="n">
         <v>60</v>
@@ -1114,22 +1114,22 @@
         <v>37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4495</v>
+        <v>0.4538</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="S4" t="n">
         <v>0.785</v>
@@ -1153,7 +1153,7 @@
         <v>0.3876</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.39837</v>
+        <v>0.39722</v>
       </c>
       <c r="AA4" t="n">
         <v>0.28125</v>
@@ -1174,7 +1174,7 @@
         <v>0.246</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AH4" t="n">
         <v>0.215</v>
@@ -1195,40 +1195,40 @@
         <v>0.28125</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.3</v>
+        <v>0.172</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6855</v>
+        <v>0.6775</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.5445</v>
+        <v>0.5325</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.6855</v>
+        <v>0.6775</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>0.3876</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6504-06-06</t>
+          <t>6504-04-06</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 9/16-18 x 9/16-18 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 7/16-20 x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1253,29 +1253,34 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1986 Overall Length = 1.590 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'L5 LGTH' = 1.590 (catalog_verified.json): equal; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1986 Hex Flat = 0.562 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'C HEX' = 0.562 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V1986 Nut Hex 1 = 0.688 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'C1 HEX' = 0.688 (catalog_verified.json): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1986 Side 1 ID = 0.172 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'B1 DRILL' = 0.172 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1986 Side 2 ID = 0.297 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'B2 DRILL' = 0.297 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'L LGTH' = 1.210 (catalog_verified.json); OMi Items!P1986 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.380; THDMAJ_B1@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U1986 "7/16-20 UNF"; catalog B1 7/16-20; THDMAJ_B2@DRIVE: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA1986 "9/16-18 UNF"; catalog B2 9/16-18; $PRP@TubeOD: OMi Items!T1986 Side 1 Size " 1/4 " + Items!Z1986 Side 2 Size " 3/8 " (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[6] thread texts, format of the built 6504 rows | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.380 vs Brennan-measured swivel -06 NOSETIP_B 0.38 (gen_straight2 SWIV_MEAS); nut hex OMi 0.688 vs SWIV_MEAS AF 0.6875</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>6504-06-06</t>
+          <t>6504-04-06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6504-06-08</t>
+          <t>6504-06-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="C5" t="n">
-        <v>0.46939</v>
+        <v>0.36084</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.625</v>
       </c>
       <c r="E5" t="n">
         <v>0.28125</v>
@@ -1320,103 +1325,103 @@
         <v>0.05556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.885</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.292</v>
+        <v>0.1465</v>
       </c>
       <c r="U5" t="n">
-        <v>0.827</v>
+        <v>0.649</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4108</v>
+        <v>0.2574</v>
       </c>
       <c r="W5" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4361</v>
+        <v>0.2796</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4499</v>
+        <v>0.3268</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.50807</v>
+        <v>0.32447</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.375</v>
+        <v>0.21875</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.34117</v>
+        <v>0.19169</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.3283</v>
+        <v>0.264</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3925</v>
+        <v>0.235</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.6723</v>
+        <v>0.5243</v>
       </c>
       <c r="AF5" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="AG5" t="n">
         <v>0.34</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0.42</v>
-      </c>
       <c r="AH5" t="n">
-        <v>0.2825</v>
+        <v>0.145</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.38338</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.3567</v>
+        <v>0.2867</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.34117</v>
+        <v>0.19169</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.375</v>
+        <v>0.21875</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AO5" t="n">
         <v>0.297</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.6605</v>
+        <v>0.6855</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.391</v>
+        <v>0.172</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.5695</v>
+        <v>0.4745</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.6605</v>
+        <v>0.6855</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.765</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.88</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.4499</v>
+        <v>0.3268</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6504-06-08</t>
+          <t>6504-06-04</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 9/16-18 x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 9/16-18 x 7/16-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1431,7 +1436,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>7/16-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1441,52 +1446,52 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows); CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1989 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1989 Side 1 ID = 0.297 (table had empty: Air-Way garbled ".030") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1989 Side 2 ID = 0.391 (table had empty: Air-Way garbled ".039") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] - batch 15, 2026-10-02 (staged, not shipped) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1987 Overall Length = 1.500 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'L5 LGTH' = 1.504 (catalog_verified.json): rounding only; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1987 Hex Flat = 0.625 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'C HEX' = 0.625 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V1987 Nut Hex 1 = 0.562 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'C1 HEX' = 0.563 (catalog_verified.json): rounding only; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1987 Side 1 ID = 0.297 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'B1 DRILL' = 0.297 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1987 Side 2 ID = 0.172 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'B2 DRILL' = 0.172 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'L LGTH' = 1.160 (catalog_verified.json); OMi Items!P1987 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.340; THDMAJ_B1@DRIVE: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U1987 "9/16-18 UNF"; catalog B1 9/16-18; THDMAJ_B2@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA1987 "7/16-20 UNF"; catalog B2 7/16-20; $PRP@TubeOD: OMi Items!T1987 Side 1 Size " 3/8 " + Items!Z1987 Side 2 Size " 1/4 " (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[4] thread texts, format of the built 6504 rows | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>D (1)/D (2) printed ".030"/".039" on Air-Way (garbled 0.30/0.39); copied as printed | D (1): printed ".030" (not a clean decimal) -&gt; left empty, MISSING | D (2): printed ".039" (not a clean decimal) -&gt; left empty, MISSING | batch 15, 2026-10-02 (staged, not shipped): D (1) / D (2) filled from OMi Items!S1989 / X1989 (0.297 / 0.391; = Brennan TFA p17 B1 / B2 DRILL, same source; Air-Way's garbled .030 / .039 read as 0.30 / 0.39 agree after rounding) -&gt; MISSING to ASSUMED. NOT changed: L13 stays Air-Way 1.65 although OMi Overall Length Items!L1989 = 1.730 is the same feature (Brennan TFA p17 drawing letter L5 = male tip to nut face, Q-B-OTHER-6504): OMi gives no L14, and OMi 1.730 with Air-Way L14 1.23 would put the swivel nose 0.50 from the nut face (Air-Way 0.42, Brennan 6500-08 STEP 0.43, catalog L5 - L 0.41); the consistent Brennan pair 1.730 / 1.32 needs the catalog L 1.32 in OMi's place (Q-NEW-CATRANK / Q-BRENNAN-ONLY) - user decision</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.340 vs Brennan-measured swivel -04 NOSETIP_B 0.35 (gen_straight2 SWIV_MEAS); nut hex OMi 0.562 vs SWIV_MEAS AF 0.5625</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>6504-06-08</t>
+          <t>6504-06-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6504-08-06</t>
+          <t>6504-06-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.46765</v>
+        <v>0.36373</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="E6" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F6" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="K6" t="n">
         <v>60</v>
@@ -1495,22 +1500,22 @@
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5367</v>
+        <v>0.4495</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="S6" t="n">
         <v>0.785</v>
@@ -1555,7 +1560,7 @@
         <v>0.246</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AH6" t="n">
         <v>0.215</v>
@@ -1576,25 +1581,25 @@
         <v>0.28125</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.796</v>
+        <v>0.6855</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.544</v>
+        <v>0.5445</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.796</v>
+        <v>0.6855</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>0.6899999999999999</v>
@@ -1604,12 +1609,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6504-08-06</t>
+          <t>6504-06-06</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 3/4-16 x 9/16-18 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 9/16-18 x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1619,7 +1624,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1639,42 +1644,42 @@
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>6504-08-06</t>
+          <t>6504-06-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6504-10-10</t>
+          <t>6504-06-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="C7" t="n">
-        <v>0.54271</v>
+        <v>0.46939</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="F7" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3553</v>
+        <v>0.2515</v>
       </c>
       <c r="H7" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="K7" t="n">
         <v>60</v>
@@ -1683,121 +1688,121 @@
         <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6213</v>
+        <v>0.4495</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.985</v>
+        <v>0.885</v>
       </c>
       <c r="T7" t="n">
-        <v>0.347</v>
+        <v>0.292</v>
       </c>
       <c r="U7" t="n">
-        <v>0.944</v>
+        <v>0.827</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4758</v>
+        <v>0.4108</v>
       </c>
       <c r="W7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4988</v>
+        <v>0.4361</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.404</v>
+        <v>0.3283</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.4475</v>
+        <v>0.3925</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.7794</v>
+        <v>0.6723</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.394</v>
+        <v>0.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.3375</v>
+        <v>0.2825</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.4364</v>
+        <v>0.3567</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.48</v>
+        <v>0.297</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.9665</v>
+        <v>0.6605</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.48</v>
+        <v>0.391</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.6935</v>
+        <v>0.5695</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.9665</v>
+        <v>0.6605</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.175</v>
+        <v>0.765</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6504-10-10</t>
+          <t>6504-06-08</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 7/8-14 x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 9/16-18 x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1807,12 +1812,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1822,47 +1827,52 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s100 only (double-pass 14 rows); CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1989 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1989 Side 1 ID = 0.297 (table had empty: Air-Way garbled ".030") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1989 Side 2 ID = 0.391 (table had empty: Air-Way garbled ".039") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] - batch 15, 2026-10-02 (staged, not shipped) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>D (1)/D (2) printed ".030"/".039" on Air-Way (garbled 0.30/0.39); copied as printed | D (1): printed ".030" (not a clean decimal) -&gt; left empty, MISSING | D (2): printed ".039" (not a clean decimal) -&gt; left empty, MISSING | batch 15, 2026-10-02 (staged, not shipped): D (1) / D (2) filled from OMi Items!S1989 / X1989 (0.297 / 0.391; = Brennan TFA p17 B1 / B2 DRILL, same source; Air-Way's garbled .030 / .039 read as 0.30 / 0.39 agree after rounding) -&gt; MISSING to ASSUMED. NOT changed: L13 stays Air-Way 1.65 although OMi Overall Length Items!L1989 = 1.730 is the same feature (Brennan TFA p17 drawing letter L5 = male tip to nut face, Q-B-OTHER-6504): OMi gives no L14, and OMi 1.730 with Air-Way L14 1.23 would put the swivel nose 0.50 from the nut face (Air-Way 0.42, Brennan 6500-08 STEP 0.43, catalog L5 - L 0.41); the consistent Brennan pair 1.730 / 1.32 needs the catalog L 1.32 in OMi's place (Q-NEW-CATRANK / Q-BRENNAN-ONLY) - user decision</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>6504-10-10</t>
+          <t>6504-06-08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6504-12-12</t>
+          <t>6504-08-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65241</v>
+        <v>0.46765</v>
       </c>
       <c r="D8" t="n">
-        <v>1.13</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="F8" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K8" t="n">
         <v>60</v>
@@ -1871,121 +1881,121 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7045</v>
+        <v>0.5367</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="R8" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="S8" t="n">
-        <v>1.089</v>
+        <v>0.785</v>
       </c>
       <c r="T8" t="n">
-        <v>0.417</v>
+        <v>0.206</v>
       </c>
       <c r="U8" t="n">
-        <v>1.047</v>
+        <v>0.735</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5928</v>
+        <v>0.3224</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2</v>
+        <v>0.145</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6237</v>
+        <v>0.3428</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5998</v>
+        <v>0.3876</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.39837</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.48614</v>
+        <v>0.25118</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.4472</v>
+        <v>0.2945</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.549</v>
+        <v>0.2925</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8623</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.481</v>
+        <v>0.246</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.4225</v>
+        <v>0.215</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.97228</v>
+        <v>0.50236</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.4851</v>
+        <v>0.3197</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.48614</v>
+        <v>0.25118</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.0525</v>
+        <v>0.796</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.7175</v>
+        <v>0.544</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.0525</v>
+        <v>0.796</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.241</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.25</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.5998</v>
+        <v>0.3876</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6504-12-12</t>
+          <t>6504-08-06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 1 1/16-12 x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 3/4-16 x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1995,12 +2005,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2015,42 +2025,42 @@
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>6504-12-12</t>
+          <t>6504-08-06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6504-16-16</t>
+          <t>6504-08-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="C9" t="n">
-        <v>0.79674</v>
+        <v>0.54155</v>
       </c>
       <c r="D9" t="n">
-        <v>1.38</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.65625</v>
+        <v>0.375</v>
       </c>
       <c r="F9" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4365</v>
+        <v>0.2837</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5965</v>
+        <v>0.3295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1292</v>
+        <v>0.0984</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="K9" t="n">
         <v>60</v>
@@ -2059,121 +2069,121 @@
         <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3125</v>
+        <v>0.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.5367</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="S9" t="n">
-        <v>1.175</v>
+        <v>0.985</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5485</v>
+        <v>0.347</v>
       </c>
       <c r="U9" t="n">
-        <v>1.139</v>
+        <v>0.944</v>
       </c>
       <c r="V9" t="n">
-        <v>0.727</v>
+        <v>0.4758</v>
       </c>
       <c r="W9" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="X9" t="n">
-        <v>0.749</v>
+        <v>0.4988</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6564</v>
+        <v>0.5265</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.86603</v>
+        <v>0.57735</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.61114</v>
+        <v>0.39884</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.4873</v>
+        <v>0.404</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.665</v>
+        <v>0.4475</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.9544</v>
+        <v>0.7794</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.604</v>
+        <v>0.394</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.5475</v>
+        <v>0.3375</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.22228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5252</v>
+        <v>0.4364</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.61114</v>
+        <v>0.39884</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.84</v>
+        <v>0.391</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.108</v>
+        <v>0.871</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.84</v>
+        <v>0.484</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.782</v>
+        <v>0.699</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.108</v>
+        <v>0.871</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.305</v>
+        <v>1.085</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.6564</v>
+        <v>0.5265</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6504-16-16</t>
+          <t>6504-08-10</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 1 5/16-12 x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 3/4-16 x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2183,12 +2193,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2198,47 +2208,52 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1992 Overall Length = 2.070 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'L5 LGTH' = 2.070 (catalog_verified.json): equal; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1992 Hex Flat = 0.938 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'C HEX' = 0.938 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V1992 Nut Hex 1 = 1.000 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'C1 HEX' = 1.000 (catalog_verified.json): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1992 Side 1 ID = 0.391 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'B1 DRILL' = 0.391 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1992 Side 2 ID = 0.484 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'B2 DRILL' = 0.484 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'L LGTH' = 1.570 (catalog_verified.json); OMi Items!P1992 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.500; THDMAJ_B1@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U1992 "3/4-16 UNF"; catalog B1 3/4-16; THDMAJ_B2@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA1992 "7/8-14 UNF"; catalog B2 7/8-14; $PRP@TubeOD: OMi Items!T1992 Side 1 Size " 1/2 " + Items!Z1992 Side 2 Size " 5/8 " (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[10] thread texts, format of the built 6504 rows | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.500 vs Brennan-measured swivel -10 NOSETIP_B 0.5 (gen_straight2 SWIV_MEAS); nut hex OMi 1.0 vs SWIV_MEAS AF 1.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>6504-16-16</t>
+          <t>6504-08-10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6504-20-20</t>
+          <t>6504-10-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.69</v>
+        <v>2.16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.97572</v>
+        <v>0.54271</v>
       </c>
       <c r="D10" t="n">
-        <v>1.69</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="F10" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4316</v>
+        <v>0.3553</v>
       </c>
       <c r="H10" t="n">
-        <v>0.753</v>
+        <v>0.386</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1288</v>
+        <v>0.1114</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2382</v>
+        <v>0.1546</v>
       </c>
       <c r="K10" t="n">
         <v>60</v>
@@ -2247,121 +2262,121 @@
         <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>1.625</v>
+        <v>0.875</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7986</v>
+        <v>0.6213</v>
       </c>
       <c r="P10" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R10" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>1.26</v>
+        <v>0.985</v>
       </c>
       <c r="T10" t="n">
-        <v>0.68</v>
+        <v>0.347</v>
       </c>
       <c r="U10" t="n">
-        <v>1.145</v>
+        <v>0.944</v>
       </c>
       <c r="V10" t="n">
-        <v>0.949</v>
+        <v>0.4758</v>
       </c>
       <c r="W10" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9889</v>
+        <v>0.4988</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5375</v>
+        <v>0.5265</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.1547</v>
+        <v>0.57735</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.76739</v>
+        <v>0.39884</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4345</v>
+        <v>0.404</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.88</v>
+        <v>0.4475</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.9556</v>
+        <v>0.7794</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.766</v>
+        <v>0.394</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.7025</v>
+        <v>0.3375</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.53478</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.4724</v>
+        <v>0.4364</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.76739</v>
+        <v>0.39884</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.69</v>
+        <v>2.16</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.08</v>
+        <v>0.48</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.194</v>
+        <v>0.9665</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.08</v>
+        <v>0.48</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.876</v>
+        <v>0.6935</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.194</v>
+        <v>0.9665</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.43</v>
+        <v>1.175</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.5375</v>
+        <v>0.5265</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6504-20-20</t>
+          <t>6504-10-10</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 1 5/8-12 x 1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 7/8-14 x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2371,12 +2386,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2391,42 +2406,42 @@
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>6504-20-20</t>
+          <t>6504-10-10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6504-24-24</t>
+          <t>6504-12-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.09</v>
+        <v>2.33</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1547</v>
+        <v>0.65241</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9375</v>
+        <v>0.53125</v>
       </c>
       <c r="F11" t="n">
         <v>0.125</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5454</v>
+        <v>0.3895</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.4715</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1298</v>
+        <v>0.1299</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2482</v>
+        <v>0.1851</v>
       </c>
       <c r="K11" t="n">
         <v>60</v>
@@ -2435,13 +2450,13 @@
         <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>1.875</v>
+        <v>1.0625</v>
       </c>
       <c r="N11" t="n">
         <v>0.08333</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9234</v>
+        <v>0.7045</v>
       </c>
       <c r="P11" t="n">
         <v>0.04511</v>
@@ -2453,136 +2468,898 @@
         <v>0.08333</v>
       </c>
       <c r="S11" t="n">
-        <v>1.41</v>
+        <v>1.089</v>
       </c>
       <c r="T11" t="n">
-        <v>0.776</v>
+        <v>0.417</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>1.047</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0504</v>
+        <v>0.5928</v>
       </c>
       <c r="W11" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1134</v>
+        <v>0.6237</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7063</v>
+        <v>0.5998</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.29904</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.9375</v>
+        <v>0.53125</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.89239</v>
+        <v>0.48614</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.5295</v>
+        <v>0.4472</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.01</v>
+        <v>0.549</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.065</v>
+        <v>0.8623</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.8885</v>
+        <v>0.481</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.4225</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.78478</v>
+        <v>0.97228</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.5674</v>
+        <v>0.4851</v>
       </c>
       <c r="AK11" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL11" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.0525</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.0525</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>6504-12-12</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 1/16-12 x 1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L13@DRIVE=2.33~2.330; CHEX@HEX=1.13~1.125; C3HEX@HEX=1.25~1.250; D1@BORE=0.61~0.609; D2@BORE=0.61~0.609</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>6504-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6504-12-16</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.79386</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="n">
+        <v>37</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.0695</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.7905</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.0695</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>6504-12-16</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 1/16-12 x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2000 Overall Length = 2.450 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'L5 LGTH' = 2.450 (catalog_verified.json): equal; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2000 Hex Flat = 1.375 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'C HEX' = 1.375 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V2000 Nut Hex 1 = 1.500 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'C1 HEX' = 1.500 (catalog_verified.json): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2000 Side 1 ID = 0.609 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'B1 DRILL' = 0.609 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2000 Side 2 ID = 0.844 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'B2 DRILL' = 0.844 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'L LGTH' = 1.860 (catalog_verified.json); OMi Items!P2000 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.590; THDMAJ_B1@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U2000 "1-1/16-12 UN"; catalog B1 1-1/16-12; THDMAJ_B2@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA2000 "1-5/16-12 UN"; catalog B2 1-5/16-12; $PRP@TubeOD: OMi Items!T2000 Side 1 Size " 3/4 " + Items!Z2000 Side 2 Size "1" (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[16] thread texts, format of the built 6504 rows | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.590 vs Brennan-measured swivel -16 NOSETIP_B 0.6 (gen_straight2 SWIV_MEAS); nut hex OMi 1.5 vs SWIV_MEAS AF 1.5</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>6504-12-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6504-16-16</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K13" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" t="n">
+        <v>37</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>6504-16-16</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 5/16-12 x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>6504-16-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6504-20-20</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.97572</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="K14" t="n">
+        <v>60</v>
+      </c>
+      <c r="L14" t="n">
+        <v>37</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>6504-20-20</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 5/8-12 x 1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>1 5/8-12</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>6504-20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6504-24-24</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K15" t="n">
+        <v>60</v>
+      </c>
+      <c r="L15" t="n">
+        <v>37</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.0504</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1134</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AB15" t="n">
         <v>0.89239</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AC15" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="AM15" t="n">
         <v>0.9375</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AN15" t="n">
         <v>3.09</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AO15" t="n">
         <v>1.312</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AP15" t="n">
         <v>1.3815</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AQ15" t="n">
         <v>1.31</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AR15" t="n">
         <v>0.9785</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AS15" t="n">
         <v>1.3815</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AT15" t="n">
         <v>1.68</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AU15" t="n">
         <v>2.25</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AV15" t="n">
         <v>0.7063</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>6504-24-24</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Male JIC x Female JIC Swivel Union, 1 7/8-12 x 1 7/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>6504</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>1 7/8-12</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>1 7/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BD15" t="inlineStr">
         <is>
           <t>D (1) printed 1.38 (D (2) 1.31); copied as printed</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BE15" t="inlineStr">
         <is>
           <t>6504-24-24</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_6504_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6504_SW2.xlsx
@@ -1658,10 +1658,10 @@
         <v>1.65</v>
       </c>
       <c r="C7" t="n">
-        <v>0.46939</v>
+        <v>0.43301</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
         <v>0.28125</v>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows); CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1989 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1989 Side 1 ID = 0.297 (table had empty: Air-Way garbled ".030") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1989 Side 2 ID = 0.391 (table had empty: Air-Way garbled ".039") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] - batch 15, 2026-10-02 (staged, not shipped) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s100 only (double-pass 14 rows); CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1989 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1989 Side 1 ID = 0.297 (table had empty: Air-Way garbled ".030") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1989 Side 2 ID = 0.391 (table had empty: Air-Way garbled ".039") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] - batch 15, 2026-10-02 (staged, not shipped); CHEX@HEX: Air-Way 0.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.813) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>D (1)/D (2) printed ".030"/".039" on Air-Way (garbled 0.30/0.39); copied as printed | D (1): printed ".030" (not a clean decimal) -&gt; left empty, MISSING | D (2): printed ".039" (not a clean decimal) -&gt; left empty, MISSING | batch 15, 2026-10-02 (staged, not shipped): D (1) / D (2) filled from OMi Items!S1989 / X1989 (0.297 / 0.391; = Brennan TFA p17 B1 / B2 DRILL, same source; Air-Way's garbled .030 / .039 read as 0.30 / 0.39 agree after rounding) -&gt; MISSING to ASSUMED. NOT changed: L13 stays Air-Way 1.65 although OMi Overall Length Items!L1989 = 1.730 is the same feature (Brennan TFA p17 drawing letter L5 = male tip to nut face, Q-B-OTHER-6504): OMi gives no L14, and OMi 1.730 with Air-Way L14 1.23 would put the swivel nose 0.50 from the nut face (Air-Way 0.42, Brennan 6500-08 STEP 0.43, catalog L5 - L 0.41); the consistent Brennan pair 1.730 / 1.32 needs the catalog L 1.32 in OMi's place (Q-NEW-CATRANK / Q-BRENNAN-ONLY) - user decision</t>
+          <t>D (1)/D (2) printed ".030"/".039" on Air-Way (garbled 0.30/0.39); copied as printed | D (1): printed ".030" (not a clean decimal) -&gt; left empty, MISSING | D (2): printed ".039" (not a clean decimal) -&gt; left empty, MISSING | batch 15, 2026-10-02 (staged, not shipped): D (1) / D (2) filled from OMi Items!S1989 / X1989 (0.297 / 0.391; = Brennan TFA p17 B1 / B2 DRILL, same source; Air-Way's garbled .030 / .039 read as 0.30 / 0.39 agree after rounding) -&gt; MISSING to ASSUMED. NOT changed: L13 stays Air-Way 1.65 although OMi Overall Length Items!L1989 = 1.730 is the same feature (Brennan TFA p17 drawing letter L5 = male tip to nut face, Q-B-OTHER-6504): OMi gives no L14, and OMi 1.730 with Air-Way L14 1.23 would put the swivel nose 0.50 from the nut face (Air-Way 0.42, Brennan 6500-08 STEP 0.43, catalog L5 - L 0.41); the consistent Brennan pair 1.730 / 1.32 needs the catalog L 1.32 in OMi's place (Q-NEW-CATRANK / Q-BRENNAN-ONLY) - user decision | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 0.813 -&gt; Air-Way 0.75</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>[BRENNAN-CELL 2026-10-20: D1@BORE] Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Brennan TFA catalog p17 table TFA-p017-t05 "MJ-FJS STRAIGHT" row 6504-24-24 col "B1 DRILL" = 1.312 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan] | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>D (1) printed 1.38 (D (2) 1.31); copied as printed</t>
+          <t>D (1) printed 1.38 (D (2) 1.31); copied as printed | 2026-10-20 D1@BORE = Brennan 1.312 (Air-Way 1.38 cannot be built: Air-Way bore 1.38 &gt;= the -24 JIC tip dia 1.381 (generator BLOCKED))</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6504_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6504_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE15"/>
+  <dimension ref="A1:BE21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,32 +2225,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6504-10-10</t>
+          <t>6504-08-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.54271</v>
+        <v>0.61315</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.062</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F10" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="H10" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="J10" t="n">
         <v>0.1546</v>
@@ -2262,121 +2262,121 @@
         <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6213</v>
+        <v>0.5367</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="R10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="S10" t="n">
-        <v>0.985</v>
+        <v>1.089</v>
       </c>
       <c r="T10" t="n">
-        <v>0.347</v>
+        <v>0.417</v>
       </c>
       <c r="U10" t="n">
-        <v>0.944</v>
+        <v>1.047</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4758</v>
+        <v>0.5928</v>
       </c>
       <c r="W10" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4988</v>
+        <v>0.6237</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5265</v>
+        <v>0.5998</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.57735</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4375</v>
+        <v>0.53125</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.39884</v>
+        <v>0.48614</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.404</v>
+        <v>0.4472</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.4475</v>
+        <v>0.549</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.7794</v>
+        <v>0.8623</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.394</v>
+        <v>0.481</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3375</v>
+        <v>0.4225</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.97228</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.4364</v>
+        <v>0.4851</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08333</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.39884</v>
+        <v>0.48614</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.4375</v>
+        <v>0.53125</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.48</v>
+        <v>0.391</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.9665</v>
+        <v>0.834</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.48</v>
+        <v>0.609</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.6935</v>
+        <v>0.696</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.9665</v>
+        <v>0.834</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.175</v>
+        <v>1.011</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.5265</v>
+        <v>0.5998</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6504-10-10</t>
+          <t>6504-08-12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 7/8-14 x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 3/4-16 x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2401,47 +2401,52 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 1993; L14 = L13 - 0.57 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[12] NOSETIP_B, Brennan-measured; Air-Way prints 0.56 / 0.57) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 1993; L14 = L13 - 0.57 (A12, end-library offset; Air-Way 0.56 / 0.57); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>6504-10-10</t>
+          <t>6504-08-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6504-12-12</t>
+          <t>6504-10-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="C11" t="n">
-        <v>0.65241</v>
+        <v>0.54098</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F11" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K11" t="n">
         <v>60</v>
@@ -2450,121 +2455,121 @@
         <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P11" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R11" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.089</v>
+        <v>0.885</v>
       </c>
       <c r="T11" t="n">
-        <v>0.417</v>
+        <v>0.292</v>
       </c>
       <c r="U11" t="n">
-        <v>1.047</v>
+        <v>0.827</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5928</v>
+        <v>0.4108</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6237</v>
+        <v>0.4361</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5998</v>
+        <v>0.4499</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.50518</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4472</v>
+        <v>0.3283</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.549</v>
+        <v>0.3925</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.8623</v>
+        <v>0.6723</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.481</v>
+        <v>0.34</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.4225</v>
+        <v>0.2825</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.97228</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.4851</v>
+        <v>0.3567</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.61</v>
+        <v>0.484</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.0525</v>
+        <v>0.9215</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.61</v>
+        <v>0.391</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.7175</v>
+        <v>0.6185</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.0525</v>
+        <v>0.9215</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.241</v>
+        <v>1.085</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.25</v>
+        <v>0.875</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.5998</v>
+        <v>0.4499</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6504-12-12</t>
+          <t>6504-10-08</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 1 1/16-12 x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 7/8-14 x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2574,67 +2579,67 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 1994; L14 = L13 - 0.43 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[8] NOSETIP_B, Brennan-measured; Air-Way prints 0.42) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L13@DRIVE=2.33~2.330; CHEX@HEX=1.13~1.125; C3HEX@HEX=1.25~1.250; D1@BORE=0.61~0.609; D2@BORE=0.61~0.609</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 1994; L14 = L13 - 0.43 (A12, end-library offset; Air-Way 0.42); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>6504-12-12</t>
+          <t>6504-10-08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6504-12-16</t>
+          <t>6504-10-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="C12" t="n">
-        <v>0.79386</v>
+        <v>0.54271</v>
       </c>
       <c r="D12" t="n">
-        <v>1.375</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F12" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K12" t="n">
         <v>60</v>
@@ -2643,121 +2648,121 @@
         <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S12" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.7794</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.9665</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.6935</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.9665</v>
+      </c>
+      <c r="AT12" t="n">
         <v>1.175</v>
       </c>
-      <c r="T12" t="n">
-        <v>0.5485</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.139</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.6564</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.86603</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.65625</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.61114</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.4873</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.9544</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.5475</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.22228</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.5252</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0.61114</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.65625</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.0695</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.7905</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.0695</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.275</v>
-      </c>
       <c r="AU12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.6564</v>
+        <v>0.5265</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6504-12-16</t>
+          <t>6504-10-10</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 1 1/16-12 x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 7/8-14 x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2767,12 +2772,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -2782,52 +2787,47 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2000 Overall Length = 2.450 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'L5 LGTH' = 2.450 (catalog_verified.json): equal; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2000 Hex Flat = 1.375 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'C HEX' = 1.375 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V2000 Nut Hex 1 = 1.500 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'C1 HEX' = 1.500 (catalog_verified.json): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2000 Side 1 ID = 0.609 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'B1 DRILL' = 0.609 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2000 Side 2 ID = 0.844 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'B2 DRILL' = 0.844 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'L LGTH' = 1.860 (catalog_verified.json); OMi Items!P2000 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.590; THDMAJ_B1@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U2000 "1-1/16-12 UN"; catalog B1 1-1/16-12; THDMAJ_B2@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA2000 "1-5/16-12 UN"; catalog B2 1-5/16-12; $PRP@TubeOD: OMi Items!T2000 Side 1 Size " 3/4 " + Items!Z2000 Side 2 Size "1" (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[16] thread texts, format of the built 6504 rows | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.590 vs Brennan-measured swivel -16 NOSETIP_B 0.6 (gen_straight2 SWIV_MEAS); nut hex OMi 1.5 vs SWIV_MEAS AF 1.5</t>
+          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>6504-12-16</t>
+          <t>6504-10-10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6504-16-16</t>
+          <t>6504-10-12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.79674</v>
+        <v>0.64952</v>
       </c>
       <c r="D13" t="n">
-        <v>1.38</v>
+        <v>1.125</v>
       </c>
       <c r="E13" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="F13" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5965</v>
+        <v>0.386</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="K13" t="n">
         <v>60</v>
@@ -2836,121 +2836,121 @@
         <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3125</v>
+        <v>0.875</v>
       </c>
       <c r="N13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.6213</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.175</v>
+        <v>1.089</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5485</v>
+        <v>0.417</v>
       </c>
       <c r="U13" t="n">
-        <v>1.139</v>
+        <v>1.047</v>
       </c>
       <c r="V13" t="n">
-        <v>0.727</v>
+        <v>0.5928</v>
       </c>
       <c r="W13" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="X13" t="n">
-        <v>0.749</v>
+        <v>0.6237</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.4873</v>
+        <v>0.4472</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.665</v>
+        <v>0.549</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.9544</v>
+        <v>0.8623</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.604</v>
+        <v>0.481</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.5475</v>
+        <v>0.4225</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.5252</v>
+        <v>0.4851</v>
       </c>
       <c r="AK13" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.84</v>
+        <v>0.484</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.108</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.84</v>
+        <v>0.609</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.782</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.108</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.305</v>
+        <v>1.231</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6504-16-16</t>
+          <t>6504-10-12</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 1 5/16-12 x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 7/8-14 x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -2975,47 +2975,52 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 1996; L14 = L13 - 0.57 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[12] NOSETIP_B, Brennan-measured; Air-Way prints 0.56 / 0.57) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 1996; L14 = L13 - 0.57 (A12, end-library offset; Air-Way 0.56 / 0.57); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>6504-16-16</t>
+          <t>6504-10-12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6504-20-20</t>
+          <t>6504-12-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="C14" t="n">
-        <v>0.97572</v>
+        <v>0.64952</v>
       </c>
       <c r="D14" t="n">
-        <v>1.69</v>
+        <v>1.125</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="F14" t="n">
         <v>0.125</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="H14" t="n">
-        <v>0.753</v>
+        <v>0.4715</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1288</v>
+        <v>0.1299</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2382</v>
+        <v>0.1851</v>
       </c>
       <c r="K14" t="n">
         <v>60</v>
@@ -3024,13 +3029,13 @@
         <v>37</v>
       </c>
       <c r="M14" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="N14" t="n">
         <v>0.08333</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7986</v>
+        <v>0.7045</v>
       </c>
       <c r="P14" t="n">
         <v>0.04511</v>
@@ -3042,103 +3047,103 @@
         <v>0.08333</v>
       </c>
       <c r="S14" t="n">
-        <v>1.26</v>
+        <v>0.985</v>
       </c>
       <c r="T14" t="n">
-        <v>0.68</v>
+        <v>0.347</v>
       </c>
       <c r="U14" t="n">
-        <v>1.145</v>
+        <v>0.944</v>
       </c>
       <c r="V14" t="n">
-        <v>0.949</v>
+        <v>0.4758</v>
       </c>
       <c r="W14" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9889</v>
+        <v>0.4988</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5375</v>
+        <v>0.5265</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.1547</v>
+        <v>0.57735</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.76739</v>
+        <v>0.39884</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.4345</v>
+        <v>0.404</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.88</v>
+        <v>0.4475</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.9556</v>
+        <v>0.7794</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.766</v>
+        <v>0.394</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.7025</v>
+        <v>0.3375</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.53478</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.4724</v>
+        <v>0.4364</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.76739</v>
+        <v>0.39884</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.08</v>
+        <v>0.609</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.194</v>
+        <v>1.0445</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.08</v>
+        <v>0.484</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.876</v>
+        <v>0.6655</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.194</v>
+        <v>1.0445</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.43</v>
+        <v>1.225</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.5375</v>
+        <v>0.5265</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6504-20-20</t>
+          <t>6504-12-10</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Male JIC x Female JIC Swivel Union, 1 5/8-12 x 1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>Male JIC x Female JIC Swivel Union, 1 1/16-12 x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -3148,12 +3153,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -3163,47 +3168,52 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 1998; L14 = L13 - 0.50 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[10] NOSETIP_B, Brennan-measured; Air-Way prints 0.49 / 0.50) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 1998; L14 = L13 - 0.50 (A12, end-library offset; Air-Way 0.49 / 0.50); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>6504-20-20</t>
+          <t>6504-12-10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6504-24-24</t>
+          <t>6504-12-12</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.09</v>
+        <v>2.33</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1547</v>
+        <v>0.65241</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9375</v>
+        <v>0.53125</v>
       </c>
       <c r="F15" t="n">
         <v>0.125</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5454</v>
+        <v>0.3895</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.4715</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1298</v>
+        <v>0.1299</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2482</v>
+        <v>0.1851</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -3212,13 +3222,13 @@
         <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.875</v>
+        <v>1.0625</v>
       </c>
       <c r="N15" t="n">
         <v>0.08333</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9234</v>
+        <v>0.7045</v>
       </c>
       <c r="P15" t="n">
         <v>0.04511</v>
@@ -3230,138 +3240,1286 @@
         <v>0.08333</v>
       </c>
       <c r="S15" t="n">
-        <v>1.41</v>
+        <v>1.089</v>
       </c>
       <c r="T15" t="n">
-        <v>0.776</v>
+        <v>0.417</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.047</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0504</v>
+        <v>0.5928</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1134</v>
+        <v>0.6237</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.7063</v>
+        <v>0.5998</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.29904</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.9375</v>
+        <v>0.53125</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.89239</v>
+        <v>0.48614</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.5295</v>
+        <v>0.4472</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.01</v>
+        <v>0.549</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.065</v>
+        <v>0.8623</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.8885</v>
+        <v>0.481</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.4225</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.78478</v>
+        <v>0.97228</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.5674</v>
+        <v>0.4851</v>
       </c>
       <c r="AK15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL15" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.0525</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.0525</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>6504-12-12</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 1/16-12 x 1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L13@DRIVE=2.33~2.330; CHEX@HEX=1.13~1.125; C3HEX@HEX=1.25~1.250; D1@BORE=0.61~0.609; D2@BORE=0.61~0.609</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>6504-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6504-12-16</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.79386</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="K16" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" t="n">
+        <v>37</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.0695</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.7905</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.0695</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>6504-12-16</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 1/16-12 x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2000 Overall Length = 2.450 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'L5 LGTH' = 2.450 (catalog_verified.json): equal; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2000 Hex Flat = 1.375 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'C HEX' = 1.375 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V2000 Nut Hex 1 = 1.500 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'C1 HEX' = 1.500 (catalog_verified.json): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2000 Side 1 ID = 0.609 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'B1 DRILL' = 0.609 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2000 Side 2 ID = 0.844 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'B2 DRILL' = 0.844 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'L LGTH' = 1.860 (catalog_verified.json); OMi Items!P2000 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.590; THDMAJ_B1@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U2000 "1-1/16-12 UN"; catalog B1 1-1/16-12; THDMAJ_B2@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA2000 "1-5/16-12 UN"; catalog B2 1-5/16-12; $PRP@TubeOD: OMi Items!T2000 Side 1 Size " 3/4 " + Items!Z2000 Side 2 Size "1" (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[16] thread texts, format of the built 6504 rows | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.590 vs Brennan-measured swivel -16 NOSETIP_B 0.6 (gen_straight2 SWIV_MEAS); nut hex OMi 1.5 vs SWIV_MEAS AF 1.5</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>6504-12-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6504-16-16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K17" t="n">
+        <v>60</v>
+      </c>
+      <c r="L17" t="n">
+        <v>37</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>6504-16-16</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 5/16-12 x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>6504-16-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6504-16-20</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.97399</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.687</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K18" t="n">
+        <v>60</v>
+      </c>
+      <c r="L18" t="n">
+        <v>37</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.1305</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.8395</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.1305</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>6504-16-20</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 5/16-12 x 1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 2003; L14 = L13 - 0.64 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[20] NOSETIP_B, Brennan-measured; Air-Way prints 0.62 / 0.63) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 2003; L14 = L13 - 0.64 (A12, end-library offset; Air-Way 0.62 / 0.63); not printed in the Brennan TFA catalog</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>6504-16-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6504-20-20</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.97572</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="K19" t="n">
+        <v>60</v>
+      </c>
+      <c r="L19" t="n">
+        <v>37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>6504-20-20</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 1 5/8-12 x 1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>1 5/8-12</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Air-Way s100 only (double-pass 14 rows) | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>6504-20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6504-24-24</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K20" t="n">
+        <v>60</v>
+      </c>
+      <c r="L20" t="n">
+        <v>37</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.0504</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.1134</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AB20" t="n">
         <v>0.89239</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AC20" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="AM20" t="n">
         <v>0.9375</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AN20" t="n">
         <v>3.09</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AO20" t="n">
         <v>1.312</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AP20" t="n">
         <v>1.3815</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AQ20" t="n">
         <v>1.31</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AR20" t="n">
         <v>0.9785</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AS20" t="n">
         <v>1.3815</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AT20" t="n">
         <v>1.68</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AU20" t="n">
         <v>2.25</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AV20" t="n">
         <v>0.7063</v>
       </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AW20" t="inlineStr">
         <is>
           <t>6504-24-24</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Male JIC x Female JIC Swivel Union, 1 7/8-12 x 1 7/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>6504</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>1 7/8-12</t>
         </is>
       </c>
-      <c r="BA15" t="inlineStr">
+      <c r="BA20" t="inlineStr">
         <is>
           <t>1 7/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr">
+      <c r="BB20" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>[BRENNAN-CELL 2026-10-20: D1@BORE] Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Brennan TFA catalog p17 table TFA-p017-t05 "MJ-FJS STRAIGHT" row 6504-24-24 col "B1 DRILL" = 1.312 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan] | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
-      <c r="BD15" t="inlineStr">
+      <c r="BD20" t="inlineStr">
         <is>
           <t>D (1) printed 1.38 (D (2) 1.31); copied as printed | 2026-10-20 D1@BORE = Brennan 1.312 (Air-Way 1.38 cannot be built: Air-Way bore 1.38 &gt;= the -24 JIC tip dia 1.381 (generator BLOCKED))</t>
         </is>
       </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BE20" t="inlineStr">
         <is>
           <t>6504-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6504-32-32</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.51554</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="K21" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" t="n">
+        <v>37</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.1734</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.65988</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.7315</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.1185</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.7315</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>6504-32-32</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Male JIC x Female JIC Swivel Union, 2 1/2-12 x 2 1/2-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>2 1/2-12</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 2007; L14 = L13 - 0.95 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[32] NOSETIP_B, Brennan-measured; Air-Way prints 0.94 (6505-32-32 only)) [ASSUMPTION logged]; thread majors from the end library; Brennan TFA p17 6504-32-32 prints L 3.700 / L5 2.862 (inconsistent: seat beyond the nut face; Q-CAT-6504-32-32-L) - not used; OMi 3.800 kept by the source order, and OMi L13 - the library offset = 2.85 = the catalog's 2.862 within 0.012; hex 2.625 / nut 2.875 / drills 1.781 equal | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 2007; L14 = L13 - 0.95 (A12, end-library offset; Air-Way 0.94 (6505-32-32 only)); Brennan TFA p17 6504-32-32 prints L 3.700 / L5 2.862 (inconsistent: seat beyond the nut face; Q-CAT-6504-32-32-L) - not used; OMi 3.800 kept by the source order, and OMi L13 - the library offset = 2.85 = the catalog's 2.862 within 0.012; hex 2.625 / nut 2.875 / drills 1.781 equal</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>6504-32-32</t>
         </is>
       </c>
     </row>
